--- a/data/availability/projects/arabia-holding/sun-capital.xlsx
+++ b/data/availability/projects/arabia-holding/sun-capital.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Fact sheet inventory for sun-capital</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1019,6 @@
       <c r="G2" t="n">
         <v>117</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1066,7 +1075,6 @@
       <c r="G3" t="n">
         <v>140</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1123,7 +1131,6 @@
       <c r="G4" t="n">
         <v>113</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1180,7 +1187,6 @@
       <c r="G5" t="n">
         <v>138</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1237,7 +1243,6 @@
       <c r="G6" t="n">
         <v>185</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1294,7 +1299,6 @@
       <c r="G7" t="n">
         <v>178</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1351,7 +1355,6 @@
       <c r="G8" t="n">
         <v>212</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1408,7 +1411,6 @@
       <c r="G9" t="n">
         <v>240</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1465,7 +1467,6 @@
       <c r="G10" t="n">
         <v>267</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
